--- a/www/download/COUNTRY.GRC.rpA2.xlsx
+++ b/www/download/COUNTRY.GRC.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Grécia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.679458599438868</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.706339394472836</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>0.800262461767013</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.866003342473462</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>0.897674167783526</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1.06845595822537</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1.11656988055068</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>1.05752964521951</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.884017000429297</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.803923181967953</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0.803793922933501</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0.796432005396897</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>0.729660721270685</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.679902072169601</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.716948695892488</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.131</t>
+          <t>4.08850998753472</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.115</t>
+          <t>3.84512503472357</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.092</t>
+          <t>3.82626064684442</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.261</t>
+          <t>3.89113467125805</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.262</t>
+          <t>3.64364991838798</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.255</t>
+          <t>3.39852381137936</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.261</t>
+          <t>3.4428774237912</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.356</t>
+          <t>2.90773182299772</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.408</t>
+          <t>2.94462255056883</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.514</t>
+          <t>2.77659471393117</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.551</t>
+          <t>2.8936533702707</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.701</t>
+          <t>2.99256240337456</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.783</t>
+          <t>2.79164837162304</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.947</t>
+          <t>2.67339948354662</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>5.035</t>
+          <t>2.60010157316117</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.406</t>
+          <t>2.8505088138183</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.405</t>
+          <t>2.57005206766109</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.403</t>
+          <t>2.58835261781403</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.518</t>
+          <t>2.52133869764637</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.574</t>
+          <t>2.25212428826321</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.595</t>
+          <t>2.02590426383754</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.644</t>
+          <t>2.21965535406599</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.744</t>
+          <t>1.84131706410117</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.797</t>
+          <t>1.8773205959778</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.903</t>
+          <t>1.67746106325743</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2.918</t>
+          <t>1.73012381873632</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.031</t>
+          <t>1.65825583628811</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1.48532406535179</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>1.48448252829265</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.091</t>
+          <t>1.42415023277383</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8769.443</t>
+          <t>0.525495032586213</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8633.201</t>
+          <t>0.481141187484175</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8451.014</t>
+          <t>0.569333553400217</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8788.894</t>
+          <t>0.587796628619175</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8982.557</t>
+          <t>0.546741119745241</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9024.035</t>
+          <t>0.506536586710348</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9037.172</t>
+          <t>0.588163571553924</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9187.541</t>
+          <t>0.375644418170865</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>9268.693</t>
+          <t>0.174899545075673</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>9400.019</t>
+          <t>0.280361171238632</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9491.005</t>
+          <t>0.30296999973017</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10097.279</t>
+          <t>0.231125086736184</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>10117.274</t>
+          <t>0.181903903882787</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>10032.667</t>
+          <t>0.131689437565958</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>10458.883</t>
+          <t>0.117059970605305</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5114.592</t>
+          <t>18436966254.8641</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5050.397</t>
+          <t>19268125163.4703</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4945.373</t>
+          <t>18004068670.545</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5210.599</t>
+          <t>18506573498.7141</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5317.495</t>
+          <t>18700998357.8547</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5369.195</t>
+          <t>20730587372.4344</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5488.763</t>
+          <t>19939224920.3581</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5677.239</t>
+          <t>20441194990.6327</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5760.728</t>
+          <t>20661265201.0776</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5936.407</t>
+          <t>21231747549.4286</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5983.249</t>
+          <t>21197733467.465</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6409.294</t>
+          <t>23252433087.8786</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>6479.312</t>
+          <t>23562651635.117</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6512.389</t>
+          <t>24100663890.1799</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6172.579</t>
+          <t>22140905502.0659</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>3930568623.60658</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>4098249599.62392</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>3949413935.02797</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24.12</t>
+          <t>4181535131.68983</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>4522222709.20582</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>4837113580.35815</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>23.86</t>
+          <t>4736351697.49119</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>5642803097.27902</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>5934338382.54562</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>26.08</t>
+          <t>6353504619.59274</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>6257132398.59612</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>6865652560.26134</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>7356720553.66807</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>7606312703.98</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>26.97</t>
+          <t>7369683053.28537</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>3768237.38665731</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>3788050.57701356</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>3919661.10960652</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>4137089.99075402</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>4072833.04215336</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4835451.50755593</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>4461850.42334551</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>40.72</t>
+          <t>4049825.75596463</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>3239277.63036677</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>43.32</t>
+          <t>2931871.15941758</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>44.09</t>
+          <t>2711453.4701736</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>2706054.16037076</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>2400548.20198479</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>2122917.66438872</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>2242013.59557618</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>48.37</t>
+          <t>40400.5976600683</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>40283.8368068354</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>39010.7265448182</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.72</t>
+          <t>40609.9403432044</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>43084.1040744749</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>43550.4408238593</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>41841.2368897133</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>42753.6294533794</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>37.19</t>
+          <t>45756.2708466277</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>52603.1759390028</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>55433.4969657395</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>33.76</t>
+          <t>61972.5945672903</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>70698.4876912798</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>32.67</t>
+          <t>76354.7177749542</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>71614.9189973366</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>80424.7999649775</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>83793.7657625142</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>77005.8619094615</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>78179.5076588859</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>81508.301306058</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>37.48</t>
+          <t>90869.657151841</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>84311.7409861908</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>87545.4604758691</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>94740.4583203738</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>105592.975997329</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>112135.529578435</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>128021.749488282</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>43.42</t>
+          <t>145431.743063438</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>162497.154980177</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>137983.246681708</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>38.98</t>
+          <t>2.37880068149996</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>2.24844378413753</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>2.35452250954127</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>2.40877028367542</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>44.02</t>
+          <t>2.25872141207475</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>2.11049698318507</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>2.23406150573122</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>1.87090557077448</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>1.7959198345048</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>1.80205324579841</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>1.8709731224922</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>1.85334431620349</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>1.71349972788208</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>1.67257236559777</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>41.14</t>
+          <t>1.62403957964167</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>23188.1171342923</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>25900.4379928804</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>25440.6005235069</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>26326.9602209037</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>28279.773219909</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>26109.0195990388</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>26244.8068278759</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>32235.9102570489</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>40148.5025167437</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>48118.0436104442</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>50696.7558147196</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>16.21</t>
+          <t>52673.3696423062</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>64730.9968994728</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>79534.767314545</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>77802.7010297477</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.679458599438868</t>
+          <t>1633.45251667255</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.706339394472836</t>
+          <t>1703.84914229597</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.800262461767013</t>
+          <t>1643.27554456786</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.866003342473462</t>
+          <t>1660.81429924267</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.897674167783526</t>
+          <t>1757.14127318697</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.06845595822537</t>
+          <t>1863.94183048822</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656988055068</t>
+          <t>1791.4526132392</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964521951</t>
+          <t>2056.38065006163</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017000429297</t>
+          <t>2121.48941319375</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923181967953</t>
+          <t>2188.65463016905</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793922933501</t>
+          <t>2144.02543259813</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796432005396897</t>
+          <t>2264.88432217658</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660721270685</t>
+          <t>2365.44187202337</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902072169601</t>
+          <t>2438.06452174744</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948695892488</t>
+          <t>2384.22907095032</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>-167792060.202929</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>210086889.524576</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>-84089133.7218109</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>-400155709.65667</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>-201895074.451173</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>888641864.028215</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>69665242.3201573</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>118498012.583624</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>272018364.192325</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1202562035.10966</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>1489800532.88369</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>2055994604.92557</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1743869692.70444</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>1557286345.98719</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>662570584.868048</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>63184964.7822677</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>418920506.598162</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>386990824.452206</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>138976980.471894</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>783664637.96455</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>2108047479.10501</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>2193300459.053</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>1797221401.2617</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>1595937643.00041</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>2671415653.25589</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>2770123356.90701</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>2925861663.02312</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>3521612360.23544</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>3667183920.54422</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>2034343474.38589</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>-230977024.985197</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>-208833617.073586</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>-471079958.174017</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>-539132690.128564</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>-985559712.415722</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-1219405615.0768</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>-2123635216.73284</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>-1678723388.67808</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>-1323919278.80809</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>-1468853618.14623</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>-1280322824.02333</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>-869867058.097554</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>-1777742667.53101</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.951</t>
+          <t>-2109897574.55703</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.926</t>
+          <t>-1371772889.51784</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>5519.11047653105</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>5534.8581553994</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>5512.40480363159</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>5661.33442996163</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>5726.03389097468</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>5797.78544056606</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>5793.66793581848</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>5903.67466389479</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>5931.51432904035</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>6132.7268103969</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>6155.43939092895</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>6462.49480754094</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>6418.6258760563</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>6515.90386636653</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>6256.31144910594</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>4901.13243838413</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>4915.92828795541</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>4941.75202087016</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>5083.09153079781</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>5257.73719217264</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>5357.69676676707</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>5382.48524598294</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>5490.9428737284</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>5534.99881524413</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>5747.91209883768</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>5784.07094247261</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>6077.71767439978</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>6045.06010425755</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>5889.05136285343</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>5950.63003340489</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>408.85</t>
+          <t>9517.20989534908</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>384.51</t>
+          <t>9875.90258828941</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>382.63</t>
+          <t>11243.1593819634</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>389.11</t>
+          <t>11441.1366680779</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>364.36</t>
+          <t>16562.4641008493</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>339.85</t>
+          <t>17852.1576033361</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>344.29</t>
+          <t>19156.7134472966</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>290.77</t>
+          <t>19530.9315061937</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>294.46</t>
+          <t>25944.0608908084</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>277.66</t>
+          <t>35763.2205205283</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>289.37</t>
+          <t>36377.8948916852</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>299.26</t>
+          <t>43164.5002693218</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>279.16</t>
+          <t>50132.4663304368</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>267.34</t>
+          <t>58538.3917396594</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>260.01</t>
+          <t>45928.476626247</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>285.05</t>
+          <t>1223283419.21464</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>257.01</t>
+          <t>1288977960.4424</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>258.84</t>
+          <t>1347188134.2032</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>252.13</t>
+          <t>1410935819.60246</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>225.21</t>
+          <t>1627927930.04994</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>202.59</t>
+          <t>2078457679.54581</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>221.97</t>
+          <t>1905125437.47278</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>184.13</t>
+          <t>1838888796.03343</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>187.73</t>
+          <t>1989364892.02972</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>167.75</t>
+          <t>2178694718.69052</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>173.01</t>
+          <t>2058508990.66151</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>165.83</t>
+          <t>2547731710.7657</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>148.53</t>
+          <t>2511103923.39864</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>148.45</t>
+          <t>2665615625.40742</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>142.42</t>
+          <t>2363536376.725</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.55</t>
+          <t>27379.0023591856</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.11</t>
+          <t>29656.0043841906</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>56.93</t>
+          <t>30845.7243839217</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>32574.0740567476</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>54.67</t>
+          <t>37335.6888861809</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>40427.1249225883</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>42303.4920150895</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>37.56</t>
+          <t>46533.9206465096</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>17.49</t>
+          <t>57366.289499536</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>67830.34461642</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>68675.0827026557</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>23.11</t>
+          <t>80437.733576592</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>18.19</t>
+          <t>98724.6647008702</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>13.17</t>
+          <t>115536.132830554</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>89996.0692386105</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20247.651</t>
+          <t>6192139889.32622</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20228.327</t>
+          <t>7066359642.11994</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20222.331</t>
+          <t>6394766282.91056</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>21660.187</t>
+          <t>6898499975.77974</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22408.297</t>
+          <t>7436351900.52977</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>22797.594</t>
+          <t>9640827273.70159</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>22932.337</t>
+          <t>9224158230.7453</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>23921.205</t>
+          <t>10399631907.5288</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>24398.391</t>
+          <t>11565270616.1382</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>25948.645</t>
+          <t>12184544360.9577</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>26320.999</t>
+          <t>11806121286.2317</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>28570.287</t>
+          <t>13362248809.4177</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>28911.612</t>
+          <t>14392128152.392</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>29131.576</t>
+          <t>14977431235.4996</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>29960.184</t>
+          <t>12298448397.1369</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13280.608</t>
+          <t>-17861.7924638365</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>13312.933</t>
+          <t>-19780.1017959012</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13248.398</t>
+          <t>-19602.5650019583</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14253.893</t>
+          <t>-21132.9373886698</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>14736.664</t>
+          <t>-20773.2247853316</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>15045.827</t>
+          <t>-22574.9673192522</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15317.653</t>
+          <t>-23146.7785677929</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>16199.955</t>
+          <t>-27002.9891403158</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>16591.934</t>
+          <t>-31422.2286087276</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>17802.858</t>
+          <t>-32067.1240958916</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>17964.059</t>
+          <t>-32297.1878109705</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>19590.071</t>
+          <t>-37273.2333072702</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>19962.459</t>
+          <t>-48592.1983704333</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>20328.421</t>
+          <t>-56997.7410908951</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>19338.34</t>
+          <t>-44067.5926123636</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18436.966</t>
+          <t>-4968856470.11158</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19268.125</t>
+          <t>-5777381681.67754</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18004.069</t>
+          <t>-5047578148.70735</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>18506.573</t>
+          <t>-5487564156.17728</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>18700.998</t>
+          <t>-5808423970.47983</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>20730.587</t>
+          <t>-7562369594.15579</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>19939.225</t>
+          <t>-7319032793.27252</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>20441.195</t>
+          <t>-8560743111.49533</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>20661.265</t>
+          <t>-9575905724.10853</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>21231.748</t>
+          <t>-10005849642.2672</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>21197.733</t>
+          <t>-9747612295.57023</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>23252.433</t>
+          <t>-10814517098.652</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>23562.652</t>
+          <t>-11881024228.9933</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>24100.664</t>
+          <t>-12311815610.0921</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>22140.906</t>
+          <t>-9934912020.41191</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>50208.82181</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>51048.6571</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>47709.23426</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>48815.60137</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>50355.49576</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>45772.90765</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>47053.17099</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>50218.51051</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>67831.47736</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>79997.73572</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>86712.20132</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>92843.80953</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>109147.8607</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>121188.13372</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>112371.99438</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>9261.626</t>
+          <t>0.107710215711266</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9263.147</t>
+          <t>0.102345594545911</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>9120.758</t>
+          <t>0.097288715639229</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>9613.144</t>
+          <t>0.0920996050398652</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>9885.076</t>
+          <t>0.0764967083446135</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>9935.398</t>
+          <t>0.0752339080694597</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>9895.203</t>
+          <t>0.078198240037305</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>9982.645</t>
+          <t>0.0613470625751352</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>9978.656</t>
+          <t>0.0705451310846372</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>10577.004</t>
+          <t>0.0712013603936523</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10478.967</t>
+          <t>0.0674462050488443</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>11256.006</t>
+          <t>0.067809663644353</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>11454.472</t>
+          <t>0.0632153662072067</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>11324.502</t>
+          <t>0.0508536906746814</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>11491.389</t>
+          <t>0.0411362156697518</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>42013.1707374524</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>43965.1707252105</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>44094.2960000242</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>44965.6765175738</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>47241.814729578</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>42409.5159224413</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42875.220364943</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>52357.9240787107</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>67858.6070569255</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>80668.4721738653</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>85337.7830020339</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>92697.5696416739</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>110178.122073115</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>127430.075197121</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>125213.580103711</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3930.569</t>
+          <t>59812.6542822835</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4098.25</t>
+          <t>62715.6626402422</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3949.414</t>
+          <t>62295.0916240648</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4181.535</t>
+          <t>63640.3871769388</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4522.223</t>
+          <t>67815.6729060742</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4837.114</t>
+          <t>60970.220312147</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4736.352</t>
+          <t>61799.5299179561</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>5642.803</t>
+          <t>74908.7324890371</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>5934.338</t>
+          <t>98041.926950747</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>6353.505</t>
+          <t>115811.88345511</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>6257.132</t>
+          <t>122932.982734002</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>6865.653</t>
+          <t>134075.134062603</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>7356.721</t>
+          <t>157280.592704313</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>7606.313</t>
+          <t>180484.72896841</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>7369.683</t>
+          <t>177848.072136483</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>237.88</t>
+          <t>335225.885817694</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>224.84</t>
+          <t>356932.075473853</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>235.45</t>
+          <t>346539.195742387</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>240.88</t>
+          <t>352321.394300357</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>225.87</t>
+          <t>368559.8096196</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>211.05</t>
+          <t>340139.918760941</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>223.41</t>
+          <t>351157.720698932</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>187.09</t>
+          <t>397789.440595074</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>179.59</t>
+          <t>515373.910056097</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>180.21</t>
+          <t>607139.36665598</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>187.1</t>
+          <t>646730.500102854</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>185.33</t>
+          <t>703683.416354248</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>171.35</t>
+          <t>824697.360216687</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>167.26</t>
+          <t>950797.044925546</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>926219.70721984</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.768</t>
+          <t>59812.6542822835</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.788</t>
+          <t>61487.3810369504</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>64807.0802257089</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4.137</t>
+          <t>67751.1583199923</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.073</t>
+          <t>72282.4949672196</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.835</t>
+          <t>74965.8991244227</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.462</t>
+          <t>75792.6269642812</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>82742.8481057962</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.239</t>
+          <t>86873.6077445838</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.932</t>
+          <t>90844.890820531</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.711</t>
+          <t>94335.9530956879</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.706</t>
+          <t>99751.5252418062</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.401</t>
+          <t>103976.826848231</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.123</t>
+          <t>110049.14255946</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.242</t>
+          <t>113859.387885602</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>42013.1707374524</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>43274.2497793281</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>45783.3205613121</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>47524.1521255572</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>49713.0725772694</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>51407.4949265036</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>51951.26907869</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>56567.0070135727</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>59148.2317585172</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>61118.0189527258</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>63135.5201386857</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>65651.5866472667</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>69587.347001906</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>73141.7950645351</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>75019.8676393409</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>59295.3696077165</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>62430.8634697578</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>59154.9537959352</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>58775.6214830612</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>56473.3854839258</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>51699.0749778529</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>53704.7225620439</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>56639.1239609629</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>76505.6225592531</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>91347.1924648905</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>94316.2737359984</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>100389.905417397</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>116864.542535687</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>127886.30613159</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>115903.874663517</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>13280607944.1243</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>13312933437.7425</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>13248397944.5473</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>14253892697.0491</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>14736663972.6597</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>15045827199.0276</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15317652702.461</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>16199954846.7618</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>16591934388.4224</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>17802858241.525</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>17964058940.2446</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>19590070709.8496</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>19962459220.4828</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>20328421136.7522</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>19338340021.2353</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>20247651450.9689</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>20228327179.4065</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>20222331231.1796</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>21660186542.1408</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>22408297149.9752</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>22797594446.935</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>22932336749.8021</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>23921204774.3118</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>24398391012.5713</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>25948644530.8615</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>26320999014.8868</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>28570287186.7604</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>28911612239.6709</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>29131575991.8069</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>29960184202.0516</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>9261626464.21733</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>9263147473.9873</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>9120757591.50051</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>9613143753.97562</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>9885076079.80919</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>9935398095.52101</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>9895203485.67614</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>9982645261.82571</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>9978656039.19299</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>10577004211.5618</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>10478966820.4792</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>11256006219.3967</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>11454472053.4127</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>11324502202.8121</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>11491388934.4534</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4131219</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4114854</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4092138</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4261223</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4261966</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4255111</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4260548</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4356484</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4408021</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4514447</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4550601</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4700825</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4782684</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4946734.91482196</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5034791.95208993</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2406295</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2405289</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2403379</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2517762</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2573625</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2595099</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2643861</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2744046</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2797251</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2902927</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2918404</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3031348</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3110083</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3119816</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3091013</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>8769442990</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8633201448</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>8451013902</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8788894157</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8982557105</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>9024035231</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9037172446</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>9187540591</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>9268692553</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>9400019109</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>9491004683</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>10097278528</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>10117273801</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>10032667395.8805</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>10458882644.303</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5114592005.43904</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>5050397458.99384</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4945373426.299</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>5210599326.69538</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>5317495219.36193</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>5369195369</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5488762918</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5677239118</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5760728069</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5936406620</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5983249244</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6409294101</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>6479312411</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6512388590</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6172579253</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.225340966083084</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.232948823909172</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.237226927667791</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.24118163639277</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.233904920813957</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.240836708288808</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.238602990085928</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.249243487413833</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.232599008054927</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.260788914447732</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.254222469856819</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.263245722347744</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.26784910933332</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.269016670729613</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.269727118190763</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.290971559363126</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.306187083248416</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.328277512911752</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.351647277091884</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.385448066759675</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.399968076680631</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.39776995231038</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.407244687140934</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.395545170131403</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.433181801876958</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.440875469224604</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.399134350888723</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.401697600956369</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.404309922144322</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.400615216883796</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.483687474553789</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.460864092842412</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.434495559420457</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.407171086515346</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.380647012426368</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.359195215030561</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.363627057603692</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.343511825445232</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.371855821813671</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.30602928367531</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.304902060918577</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.337619926763533</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.330453289710311</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.326673407126065</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.329657664925441</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.371346947245537</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.377495351521338</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.380895490214712</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.383899325003038</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.366128130166343</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.374798240107462</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.371233029195161</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.379927010715208</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.384015821018181</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.401867741789303</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.397578739785172</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.42497703068806</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.434158894495118</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.436895912157739</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.438482748779813</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.389806732039504</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.392942559839754</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.403611401366628</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.413953244239236</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.440242378161553</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.437661274948664</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.437818078117429</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.442544999518498</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.446890749089195</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.448678263348279</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.454417753572607</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.412947613463164</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.409051402200585</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.414293168663199</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.411364260838987</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.238846320714959</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.229562088638908</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.21549310841866</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.202147430757726</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.193629491672104</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.187540484943875</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.19094889268741</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.177527989766294</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.169093429892624</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.149453994862418</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.148003506642221</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.162075355848776</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.156789703304298</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.148810919179061</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.1501529903812</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>213345.15517</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>223447.60162</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>213900.888</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>213400.04529</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>217235.41692</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>202218.87014</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>206975.0654</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>235578.53858</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>303339.46095</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>356814.39674</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>374855.13439</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>407994.35689</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>478252.47301</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>537862.71926</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>489053.61632</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>119108.02389</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>125146.52611</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>121450.04542</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>122416.00866</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>124289.05839</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>112669.29529</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>115504.25248</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>131547.85645</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>174547.54951</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>207159.07592</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>217249.25647</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>234465.03948</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>274145.13524</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>308371.0351</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>293751.9468</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>227772.109671182</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>237366.924976616</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>247726.647313983</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>259588.099334434</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>273162.506765273</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>287944.533978578</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>303214.490316467</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>320489.563175503</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>340228.312234553</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>359268.411014974</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>375676.26822843</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>394358.77688263</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>414661.433611407</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>431763.149905656</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>444746.318180714</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
